--- a/智能高速隔离USB Hub/制作图纸和BOM/BOM_HUB底板_Schematic1_2026-05-26.xlsx
+++ b/智能高速隔离USB Hub/制作图纸和BOM/BOM_HUB底板_Schematic1_2026-05-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BF8A0C-DAB4-4A82-918B-3FF1B9A5608E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593EFBD-E1FE-4BC8-808B-41B6BC587589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1967,7 +1967,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="7" t="s">
         <v>138</v>
       </c>
       <c r="B25">
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>203</v>
       </c>
       <c r="B37">

--- a/智能高速隔离USB Hub/制作图纸和BOM/BOM_HUB底板_Schematic1_2026-05-26.xlsx
+++ b/智能高速隔离USB Hub/制作图纸和BOM/BOM_HUB底板_Schematic1_2026-05-26.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593EFBD-E1FE-4BC8-808B-41B6BC587589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686240E8-C300-4757-BEAC-ABA1A9488394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -767,7 +767,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -803,6 +803,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -852,7 +859,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1330,10 +1337,10 @@
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
@@ -1682,10 +1689,10 @@
       <c r="A16" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D16" t="s">
@@ -1967,7 +1974,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>138</v>
       </c>
       <c r="B25">
